--- a/coronavirus_response_forms/020_return_to_training_waiver--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/020_return_to_training_waiver--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Return To Training Waiver</t>
+          <t>Purpose of this form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Output File</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>description_brief</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Brief Description</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>description_long</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Long Description</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description_long</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description (Long)</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>description_long</t>
+          <t>form_title</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description (Long)</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,62 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>coronavirus_response_forms</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Coronavirus Response Forms</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -895,36 +849,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>assessment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Assessment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>certification</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Certification</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -975,24 +929,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>coronavirus_response_forms</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coronavirus Response Forms</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1009,32 +963,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>assessment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>category_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>certification</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>category_2_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
